--- a/artfynd/A 25341-2026 artfynd.xlsx
+++ b/artfynd/A 25341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136188216</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136188215</v>
       </c>
       <c r="B3" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136188217</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25341-2026 artfynd.xlsx
+++ b/artfynd/A 25341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136188216</v>
       </c>
       <c r="B2" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136188215</v>
       </c>
       <c r="B3" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136188217</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25341-2026 artfynd.xlsx
+++ b/artfynd/A 25341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136188216</v>
       </c>
       <c r="B2" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136188215</v>
       </c>
       <c r="B3" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136188217</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25341-2026 artfynd.xlsx
+++ b/artfynd/A 25341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136188216</v>
       </c>
       <c r="B2" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136188215</v>
       </c>
       <c r="B3" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136188217</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25341-2026 artfynd.xlsx
+++ b/artfynd/A 25341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136188216</v>
       </c>
       <c r="B2" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136188215</v>
       </c>
       <c r="B3" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136188217</v>
       </c>
       <c r="B4" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25341-2026 artfynd.xlsx
+++ b/artfynd/A 25341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136188216</v>
       </c>
       <c r="B2" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136188215</v>
       </c>
       <c r="B3" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136188217</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25341-2026 artfynd.xlsx
+++ b/artfynd/A 25341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136188216</v>
       </c>
       <c r="B2" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136188215</v>
       </c>
       <c r="B3" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136188217</v>
       </c>
       <c r="B4" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25341-2026 artfynd.xlsx
+++ b/artfynd/A 25341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136188216</v>
       </c>
       <c r="B2" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136188215</v>
       </c>
       <c r="B3" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136188217</v>
       </c>
       <c r="B4" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25341-2026 artfynd.xlsx
+++ b/artfynd/A 25341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136188216</v>
       </c>
       <c r="B2" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136188215</v>
       </c>
       <c r="B3" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136188217</v>
       </c>
       <c r="B4" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
